--- a/Dragons-Trail-China-7-Day-Itinerary.xlsx
+++ b/Dragons-Trail-China-7-Day-Itinerary.xlsx
@@ -16,6 +16,7 @@
     <sheet name="Phrases" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Packing" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="FAQ" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Beijing Trail" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Itinerary'!$A$3:$G$3</definedName>
@@ -26,9 +27,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;₹&quot;#,##0;(&quot;₹&quot;#,##0);-"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -238,7 +240,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
@@ -428,6 +430,21 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -809,7 +826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -875,7 +892,7 @@
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>DAY 1  ·  Wheels Up, First Bite of Beijing  —  Mumbai → Beijing · hutongs, duck, and the world’s largest public square</t>
+          <t>DAY 1  ·  Straight Up the Central Axis  —  Land → Peking duck → Tiananmen → Forbidden City → Jingshan sunset → hutongs → Wangfujing</t>
         </is>
       </c>
     </row>
@@ -900,7 +917,7 @@
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>There is no non-stop from Mumbai to Beijing, so you fly one-stop — Hong Kong, Bangkok or Kuala Lumpur are the sensible hubs, and the overnight departure is the one that protects your first day. Book 8–10 weeks out on a Tue/Wed for the ₹36–40k round-trip open-jaw (into Beijing PEK, out of Shanghai PVG). An open-jaw costs the same as a return and saves you a 1,200 km backtrack.</t>
+          <t>There is no non-stop from Mumbai to Beijing, so you fly one-stop — Hong Kong, Bangkok or Kuala Lumpur are the sensible hubs, and the overnight departure is the one that protects your first day. Book 8–10 weeks out on a Tue/Wed for the ₹36–40k round-trip open-jaw (into Beijing PEK, out of Shanghai PVG).</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
@@ -933,7 +950,7 @@
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Long enough to be safe, short enough that you are not sleeping in a terminal. Stay airside, do not collect bags — book it as ONE ticket so the connection is the airline’s problem, not yours. This is worth paying ₹2,000 more for.</t>
+          <t>Long enough to be safe, short enough that you are not sleeping in a terminal. Stay airside, do not collect bags — book it as ONE ticket so the connection is the airline’s problem, not yours.</t>
         </is>
       </c>
       <c r="F6" s="15" t="inlineStr">
@@ -1032,7 +1049,7 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Buy a Yikatong transit card at the station (¥20 deposit, refundable) or just scan the Alipay transit QR. Airport Express ¥25, 20 min. Total door-to-door about 70 minutes.</t>
+          <t>Buy a Yikatong transit card at the station (¥20 deposit, refundable) or just scan the Alipay transit QR. Airport Express ¥25, 20 min, then Line 2 around the old city wall to Qianmen. About 70 minutes door to door.</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
@@ -1065,7 +1082,7 @@
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Check-in is 14:00 but every Beijing hotel will hold luggage. Stay in the Qianmen/Dashilan area — you are 900 m from Tiananmen and inside a real hutong grid.</t>
+          <t>Check-in is 14:00 but every Beijing hotel will hold luggage. You are staying in Qianmen — 900 m south of Tiananmen, at the bottom of the Central Axis you are about to walk all the way up.</t>
         </is>
       </c>
       <c r="F10" s="15" t="inlineStr">
@@ -1093,12 +1110,12 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>13:20  Lunch: Peking duck at Siji Minfu (Qianmen branch)</t>
+          <t>13:10  Peking duck at Siji Minfu (Qianmen branch)</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>The locals’ answer to Quanjude, at half the price. A whole duck is ¥208 and feeds two comfortably — crisp lacquered skin dipped in caster sugar first, then meat rolled in pancakes with scallion and sweet bean sauce. Get a queue ticket the moment you arrive; the wait is 40 min at peak and worth every minute.</t>
+          <t>The locals’ answer to Quanjude, at half the price, and a five-minute walk from the hotel. A whole duck is ¥208 and feeds two comfortably — crisp lacquered skin dipped in caster sugar first, then meat rolled in pancakes with scallion and sweet bean sauce. Take a queue ticket the moment you arrive; the wait is 40 min at peak. Doing the duck now, on day one, means it is never the thing you ran out of days for.</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
@@ -1126,17 +1143,17 @@
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>15:00  Check in + a strategic 45-minute nap</t>
+          <t>14:30  Tiananmen Square</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Non-negotiable. You have barely slept on a red-eye and Day 2 starts at 06:45. Set two alarms.</t>
+          <t>Free, but you MUST reserve a passport-linked slot on the official WeChat mini-program 1–7 days ahead — walk-ups are turned away. Security is airport-grade. The square is 440,000 m²: Monument to the People’s Heroes in the middle, Mao’s Mausoleum south, the Great Hall of the People west, the National Museum east. Walk north through it toward the Gate of Heavenly Peace.</t>
         </is>
       </c>
       <c r="F12" s="15" t="inlineStr">
         <is>
-          <t>Stay</t>
+          <t>Book ahead</t>
         </is>
       </c>
       <c r="G12" s="16" t="n">
@@ -1159,17 +1176,17 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>16:00  Tiananmen Square</t>
+          <t>15:15  Add-on: National Museum of China</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>Free, but you MUST reserve a passport-linked slot on the official WeChat mini-program 1–7 days ahead — walk-ups are turned away. Security is airport-grade. The square is 440,000 m²: Monument to the People’s Heroes in the middle, Mao’s Mausoleum south, the Great Hall of the People west.</t>
+          <t>On the east side of the square, free with a passport booking, and genuinely world-class — 1.4 million objects, with the Houmuwu bronze ding and the jade burial suits in the "Ancient China" basement. BUT: it needs 90 minutes minimum, last entry is 16:00, and taking it today costs you the Jingshan sunset. Do it only if your flight landed early, or on a return trip. The honest call on a seven-day itinerary is to skip it.</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>Book ahead</t>
+          <t>Optional</t>
         </is>
       </c>
       <c r="G13" s="10" t="n">
@@ -1192,21 +1209,21 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>17:00  Dashilan &amp; Yangmeizhu Xiejie hutong walk</t>
+          <t>15:20  The Forbidden City</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Skip the sanitised main drag. Duck west into Yangmeizhu Xiejie — a 500-year-old slanted lane now full of independent bookshops (try Modernista), tiny galleries and grandmothers playing xiangqi. This is the Beijing that the Forbidden City queue never sees.</t>
+          <t>Enter at the Meridian Gate (Wumen) — last admission is 16:00, so this is the hard deadline of your day. It is one-way: Gate of Supreme Harmony → the Three Great Halls on their triple marble terrace → Palace of Heavenly Purity → Imperial Garden → out at the Gate of Divine Prowess (Shenwumen). Two and a bit hours at pace. If you have time in hand, cut east into the Treasure Gallery (¥10) for the Nine Dragon Screen. 9,000 rooms, 24 emperors, 1420–1912.</t>
         </is>
       </c>
       <c r="F14" s="15" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>UNESCO</t>
         </is>
       </c>
       <c r="G14" s="16" t="n">
-        <v>0</v>
+        <v>830</v>
       </c>
     </row>
     <row r="15" ht="42" customHeight="1">
@@ -1225,21 +1242,21 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>18:15  Zhengyangmen Gate at blue hour</t>
+          <t>17:40  Jingshan Park — the view that makes the day</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>The 40 m Ming gate tower at the square’s south end lights up around sunset. Stand on the Qianmen pedestrian street looking north — gate, tram tracks and lanterns all in one frame. The photograph of the trip, taken on Day 1.</t>
+          <t>¥2, and it is directly across the road from the exit you just walked out of. Fifteen minutes up an artificial hill built from the earth dug out of the palace moat, and from the Wanchun Pavilion the entire Forbidden City unrolls south beneath you in perfect symmetry, roof after golden roof, with the Beijing skyline stacked behind. Come at sunset and you share it with a crowd; it is still the single best view in the city.</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>Photo</t>
+          <t>Best view</t>
         </is>
       </c>
       <c r="G15" s="10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" ht="42" customHeight="1">
@@ -1258,21 +1275,21 @@
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>19:30  Dinner: zhajiangmian in the alley</t>
+          <t>18:40  Hutong lanes — Nanluoguxiang &amp; the Shichahai alleys</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>Old Beijing fried-sauce noodles at Fangzhuanchang Zhajiangmian — ¥22, hand-pulled, buried under eight little dishes of julienned vegetables you tip in and thrash together. Add a bowl of douzhi (fermented mung-bean drink) if you are brave; it tastes like a dare.</t>
+          <t>Walk north-east off Jingshan into the real grey-brick grid. Nanluoguxiang is the famous one — 800 years old, now busy and commercial — so use it as a spine and duck into the quieter side hutongs running off it: Mao’er, Ju’er, Qianyuan’ensi. Grandmothers playing xiangqi, courtyard doors with their original stone drums, laundry over the lanes. Keep walking west and you hit the Shichahai lakes and the Drum and Bell Towers.</t>
         </is>
       </c>
       <c r="F16" s="15" t="inlineStr">
         <is>
-          <t>Cheap eat</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="G16" s="16" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" ht="42" customHeight="1">
@@ -1291,84 +1308,84 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>21:00  Wangfujing night stroll, then sleep</t>
+          <t>19:45  Wangfujing night walk</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>A 15-minute metro hop for the neon, the Xinhua bookstore and a last street snack. In bed by 22:30 — tomorrow is the biggest walking day of the week.</t>
+          <t>Metro two stops south-east, or a ¥20 Didi. Beijing’s big pedestrian shopping street at full neon: the flagship Xinhua bookstore, the old Wangfujing snack lanes, tanghulu (candied hawthorn on a stick) from a cart, and the Oriental Plaza windows. A gentle, lit, entirely undemanding end to a day that started on an aeroplane.</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Night</t>
         </is>
       </c>
       <c r="G17" s="10" t="n">
         <v>120</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="17" t="inlineStr"/>
-      <c r="B18" s="17" t="inlineStr"/>
-      <c r="C18" s="17" t="inlineStr"/>
-      <c r="D18" s="18" t="inlineStr">
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>Day 1</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>21:15  Line 1 → Line 2 back to Qianmen, and sleep</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="inlineStr">
+        <is>
+          <t>Twelve minutes on the metro. You have been awake for about 26 hours and covered nine and a half kilometres on foot. Tomorrow starts at 06:15.</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>Rest</t>
+        </is>
+      </c>
+      <c r="G18" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr"/>
+      <c r="B19" s="17" t="inlineStr"/>
+      <c r="C19" s="17" t="inlineStr"/>
+      <c r="D19" s="18" t="inlineStr">
         <is>
           <t>Day 1 — activities subtotal</t>
         </is>
       </c>
-      <c r="E18" s="19" t="inlineStr">
+      <c r="E19" s="19" t="inlineStr">
         <is>
           <t>Hotel that night: Qianmen hutong hostel / 3★</t>
         </is>
       </c>
-      <c r="F18" s="19" t="inlineStr">
+      <c r="F19" s="19" t="inlineStr">
         <is>
           <t>Stay ₹2,400</t>
         </is>
       </c>
-      <c r="G18" s="20" t="n">
-        <v>2210</v>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>DAY 2  ·  Imperial Beijing, End to End  —  Temple of Heaven at dawn → Forbidden City → the rooftop view → Houhai lakes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="42" customHeight="1">
-      <c r="A21" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>Day 2</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>Beijing</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>06:45  Breakfast: jianbing from the cart</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>A crêpe of mung-bean batter cracked with an egg, painted with chilli and fermented bean paste, folded around a sheet of shattering fried cracker. ¥8. Point at what the person ahead of you got.</t>
-        </is>
-      </c>
-      <c r="F21" s="9" t="inlineStr">
-        <is>
-          <t>Street food</t>
-        </is>
-      </c>
-      <c r="G21" s="10" t="n">
-        <v>100</v>
+      <c r="G19" s="20" t="n">
+        <v>2690</v>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>DAY 2  ·  Dawn Ritual, Imperial Garden, Olympic Neon  —  Temple of Heaven at sunrise → Summer Palace → Bird’s Nest &amp; Water Cube lit up → sesame hotpot</t>
+        </is>
       </c>
     </row>
     <row r="22" ht="42" customHeight="1">
@@ -1387,21 +1404,21 @@
       </c>
       <c r="D22" s="13" t="inlineStr">
         <is>
-          <t>07:30  Temple of Heaven — enter by the East Gate</t>
+          <t>06:15  Breakfast: jianbing from the cart</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
         <is>
-          <t>Go at opening (06:00 park / 08:00 halls) for the reason nobody tells you: the surrounding park is Beijing’s living room. Retired couples ballroom-dance under the cypresses, a 60-strong choir belts revolutionary songs, men play jianzi and hang from trees. Then walk the raised Danbi Bridge north to the Hall of Prayer for Good Harvests — a triple-eaved cobalt-blue rotunda built in 1420 without a single nail.</t>
+          <t>A crêpe of mung-bean batter cracked with an egg, painted with chilli and fermented bean paste, folded around a sheet of shattering fried cracker. ¥8. Point at what the person ahead of you got.</t>
         </is>
       </c>
       <c r="F22" s="15" t="inlineStr">
         <is>
-          <t>UNESCO</t>
+          <t>Street food</t>
         </is>
       </c>
       <c r="G22" s="16" t="n">
-        <v>420</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" ht="42" customHeight="1">
@@ -1420,21 +1437,21 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>09:45  Metro Line 5 → Line 1 → Tiananmen East</t>
+          <t>06:45  Temple of Heaven — enter by the East Gate</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>¥4, 25 minutes. Beijing’s metro is spotless, signed in English and impossible to get lost on. Avoid 08:00–09:00 unless you enjoy being compressed.</t>
+          <t>The park opens at 06:00 and the halls at 08:00, and the gap is the whole point: this is Beijing’s living room at its best hour. Then walk the raised Danbi Bridge north to the Hall of Prayer for Good Harvests — a triple-eaved cobalt-blue rotunda built in 1420, 38 m tall, and assembled without a single nail. Buy the ¥34 through-ticket, not the ¥15 park-only.</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>UNESCO</t>
         </is>
       </c>
       <c r="G23" s="10" t="n">
-        <v>50</v>
+        <v>420</v>
       </c>
     </row>
     <row r="24" ht="42" customHeight="1">
@@ -1453,21 +1470,21 @@
       </c>
       <c r="D24" s="13" t="inlineStr">
         <is>
-          <t>10:15  The Forbidden City — 3.5 hours, and earn them</t>
+          <t>09:30  Cross the city: Line 5 → Line 10 → Line 4 to Beigongmen</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
         <is>
-          <t>Enter at the Meridian Gate (Wumen), exit at the Gate of Divine Prowess (Shenwumen) — one-way only, so there is no doubling back. Spine route: Gate of Supreme Harmony → the Three Great Halls on their triple marble terrace → Palace of Heavenly Purity → Imperial Garden. Then break the pattern everyone else follows: cut east into the Treasure Gallery (¥10) for the Nine Dragon Screen and the imperial jade, and the Clock &amp; Watch Gallery for the absurd European automata the Qianlong Emperor collected. 9,000 rooms, 24 emperors, 1420–1912.</t>
+          <t>The long transit of the trip — about 75 minutes and ¥6 from the far south of the city to the far north-west. Sit down, charge your phone, eat the second jianbing you should have bought. Get out at Beigongmen for the Summer Palace’s North Palace Gate, which puts you at the quiet back entrance rather than the coach-park one.</t>
         </is>
       </c>
       <c r="F24" s="15" t="inlineStr">
         <is>
-          <t>UNESCO</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="G24" s="16" t="n">
-        <v>830</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" ht="42" customHeight="1">
@@ -1486,21 +1503,21 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>13:45  Lunch: Qingfeng Baozi near Beihai</t>
+          <t>11:00  The Summer Palace</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>The steamed-bun chain a Chinese president famously queued at. Pork-and-onion buns ¥6 for six, plus a bowl of chao gan (liver-and-intestine stew) if you want the full old-Beijing experience. Fast, ₹200, and you need to keep moving.</t>
+          <t>¥60 through-ticket. Three-quarters of it is water. Enter at the north gate, come down over Longevity Hill past the Tower of Buddhist Incense, then walk the Long Corridor — 728 m of covered walkway with 14,000 individually painted scenes — along the shore of Kunming Lake to the Marble Boat. This was where the Qing court escaped the summer, and Cixi famously rebuilt it with money earmarked for the navy. Give it three hours; it is enormous and it deserves them.</t>
         </is>
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>Cheap eat</t>
+          <t>UNESCO</t>
         </is>
       </c>
       <c r="G25" s="10" t="n">
-        <v>260</v>
+        <v>710</v>
       </c>
     </row>
     <row r="26" ht="42" customHeight="1">
@@ -1519,21 +1536,21 @@
       </c>
       <c r="D26" s="13" t="inlineStr">
         <is>
-          <t>14:30  Jingshan Park — the view that makes the day</t>
+          <t>13:00  Lunch by Kunming Lake</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>¥2 and a 15-minute climb up an artificial hill built from the earth dug out of the palace moat. From the Wanchun Pavilion the entire Forbidden City unrolls south beneath you in perfect symmetry, roof after golden roof, with the Beijing skyline stacked behind. Go now, not at sunset — by 17:00 the pavilion is shoulder to shoulder.</t>
+          <t>Tingliguan ("Listening to Orioles") inside the grounds is the atmospheric option and priced accordingly; the canteen near the Suzhou Street bridge does a good ¥40 bowl of noodles. Then take the ¥15 ferry across the lake to the Seventeen-Arch Bridge and the bronze ox rather than walking around it.</t>
         </is>
       </c>
       <c r="F26" s="15" t="inlineStr">
         <is>
-          <t>Best view</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="G26" s="16" t="n">
-        <v>30</v>
+        <v>450</v>
       </c>
     </row>
     <row r="27" ht="42" customHeight="1">
@@ -1552,21 +1569,21 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>15:45  Beihai Park &amp; the White Dagoba</t>
+          <t>15:30  Line 4 → Line 10 → Line 8 to Olympic Green</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>¥10. An imperial pleasure garden from the 11th century built around a lake, crowned by a Tibetan-style white stupa. Rent a pedal boat for ¥60/hour if the legs need a rest — from the water you get the dagoba, the willows and the Forbidden City rooftops in one shot.</t>
+          <t>About 55 minutes east across the top of the city. You are heading for the 2008 Olympic Park, which sits on the northern end of the same Central Axis you walked up yesterday — the line runs from the Temple of Heaven in the south, through Tiananmen and the Forbidden City, to the Bird’s Nest. Seven hundred years of city planning, one straight line.</t>
         </is>
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>Park</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="G27" s="10" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" ht="42" customHeight="1">
@@ -1585,12 +1602,12 @@
       </c>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>17:15  Shichahai &amp; Houhai lakes, via Yandaixie Street</t>
+          <t>16:45  Olympic Green — arrive in daylight first</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>Beijing’s oldest commercial hutong (700 years) — "Tobacco Pouch Slant Street" — spills you out onto the lakes. Cross the Silver Ingot Bridge, then walk north to the Drum and Bell Towers standing back-to-back in their own plaza, where they have kept the city’s time since Kublai Khan.</t>
+          <t>Free and enormous. Walk the plaza between the two buildings while it is still light so you get them both in daylight and again lit, then find the Olympic Tower and the dragon-shaped water feature. There is a food court under the plaza if you want a snack to hold you to the hotpot.</t>
         </is>
       </c>
       <c r="F28" s="15" t="inlineStr">
@@ -1618,21 +1635,21 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>18:45  Sunset beer on the Houhai waterfront</t>
+          <t>18:30  Bird’s Nest &amp; Water Cube lit up</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>A Yanjing at a lakeside table for ¥15 while the willows go black and the bar-street neon comes up on the far bank. Skip the live-music bars themselves — overpriced, and you have an early start.</t>
+          <t>The reason you came at this hour. The Bird’s Nest — 42,000 tonnes of interwoven steel by Herzog &amp; de Meuron — glows red from inside its lattice. Two hundred metres away the Water Cube’s ETFE bubble skin cycles through blues, purples and greens on a slow loop. Exteriors are free and the plaza between them is the shot. Going inside the stadium is ¥80 and honestly unnecessary.</t>
         </is>
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>Chill</t>
+          <t>Iconic</t>
         </is>
       </c>
       <c r="G29" s="10" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" ht="42" customHeight="1">
@@ -1651,21 +1668,21 @@
       </c>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>19:45  Dinner: old Beijing copper-pot mutton hotpot</t>
+          <t>19:40  Line 8 straight home to Qianmen</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t>Not the fiery Sichuan version — the Beijing one: a brass chimney pot of clear broth with ginger and jujube, paper-thin hand-cut mutton swirled for eight seconds, dunked in a sesame-paste sauce you mix yourself. Try Julong Zhai or Nanmen Shuan Rou. ₹700 a head with beer.</t>
+          <t>One of the great conveniences of Beijing: Line 8 runs directly down the Central Axis from Olympic Green to Qianmen with no changes. Thirty-five minutes, ¥5.</t>
         </is>
       </c>
       <c r="F30" s="15" t="inlineStr">
         <is>
-          <t>Must-eat</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="G30" s="16" t="n">
-        <v>720</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31" ht="42" customHeight="1">
@@ -1684,84 +1701,84 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>21:30  Optional: Kung-fu at the Red Theatre</t>
+          <t>20:20  Beijing sesame hotpot (shuàn yángròu)</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>The Legend of Kung Fu, 80 minutes, ¥180 for a rear-stalls seat. Touristy and completely enjoyable. Skip it and sleep if the day has eaten you — Day 3 is the Wall.</t>
+          <t>Not the fiery Sichuan version — the Beijing one, and the sesame is the point. A brass chimney pot of clear broth with ginger and jujube arrives at the table; you swirl paper-thin hand-cut mutton for eight seconds and drop it into a bowl of sesame paste you mix yourself with fermented bean curd, chive flower sauce, coriander and chilli oil. Julong Zhai or Nanmen Shuan Rou are the old names. ₹700 a head with beer, and exactly what 15 km of walking has earned you.</t>
         </is>
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Must-eat</t>
         </is>
       </c>
       <c r="G31" s="10" t="n">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="32" ht="42" customHeight="1">
+      <c r="A32" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B32" s="12" t="inlineStr">
+        <is>
+          <t>Day 2</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>22:00  Back to the hotel — repack tonight</t>
+        </is>
+      </c>
+      <c r="E32" s="14" t="inlineStr">
+        <is>
+          <t>Tomorrow you leave for the Wall at 06:40 and board a night train at 20:37, so split your luggage now: daypack for the Wall, big bag left at reception.</t>
+        </is>
+      </c>
+      <c r="F32" s="15" t="inlineStr">
+        <is>
+          <t>Rest</t>
+        </is>
+      </c>
+      <c r="G32" s="16" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="17" t="inlineStr"/>
-      <c r="B32" s="17" t="inlineStr"/>
-      <c r="C32" s="17" t="inlineStr"/>
-      <c r="D32" s="18" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="17" t="inlineStr"/>
+      <c r="B33" s="17" t="inlineStr"/>
+      <c r="C33" s="17" t="inlineStr"/>
+      <c r="D33" s="18" t="inlineStr">
         <is>
           <t>Day 2 — activities subtotal</t>
         </is>
       </c>
-      <c r="E32" s="19" t="inlineStr">
+      <c r="E33" s="19" t="inlineStr">
         <is>
           <t>Hotel that night: Qianmen hutong hostel / 3★</t>
         </is>
       </c>
-      <c r="F32" s="19" t="inlineStr">
+      <c r="F33" s="19" t="inlineStr">
         <is>
           <t>Stay ₹2,400</t>
         </is>
       </c>
-      <c r="G32" s="20" t="n">
-        <v>2790</v>
-      </c>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>DAY 3  ·  The Great Wall, Then a Night Train  —  Mutianyu ridgeline → toboggan down → 798 Art Zone → overnight sleeper to Xi’an</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="42" customHeight="1">
-      <c r="A35" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>Day 3</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>Beijing</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>06:00  Check out, leave the big bag at reception</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t>You are on a night train tonight, so travel light to the Wall — daypack, 2 L water, layers. The hotel will hold the main bag until 19:00 free of charge; confirm this when you check in on Day 1.</t>
-        </is>
-      </c>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t>Logistics</t>
-        </is>
-      </c>
-      <c r="G35" s="10" t="n">
-        <v>0</v>
+      <c r="G33" s="20" t="n">
+        <v>2560</v>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>DAY 3  ·  The Great Wall, Then a Night Train  —  Mutianyu ridgeline → toboggan down → back to Beijing → overnight sleeper to Xi’an</t>
+        </is>
       </c>
     </row>
     <row r="36" ht="42" customHeight="1">
@@ -1780,21 +1797,21 @@
       </c>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>06:40  Bus 916 Express: Dongzhimen → Huairou</t>
+          <t>05:45  Check out, leave the big bag at reception</t>
         </is>
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>The cheapest honest way to the Wall — ¥12, 70 minutes, air-conditioned. At Huairou Beidajie, switch to the h23/h24 local bus or split a taxi (¥40 for the car) the last 12 km to Mutianyu. Ignore the men shouting "Great Wall! Great Wall!" at the bus door — they will quote ¥400.</t>
+          <t>You are on a night train tonight, so travel light to the Wall — daypack, 2 L water, layers. The hotel will hold the main bag until 19:00 free of charge; confirm this when you check in on Day 1.</t>
         </is>
       </c>
       <c r="F36" s="15" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="G36" s="16" t="n">
-        <v>340</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" ht="42" customHeight="1">
@@ -1813,21 +1830,21 @@
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>08:45  Mutianyu Great Wall — ticket + cable car up</t>
+          <t>06:40  Bus 916 Express: Dongzhimen → Huairou</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>Mutianyu over Badaling, always: 2,250 m of fully restored Ming wall, 22 watchtowers, forested mountains on both sides, and a third of the crowd. Entry ¥45, shuttle ¥15, cable car ¥100 one-way. Take the cable car UP to Watchtower 14 and save your legs for the ridgeline.</t>
+          <t>The cheapest honest way to the Wall — ¥12, 70 minutes, air-conditioned. At Huairou Beidajie, switch to the h23/h24 local bus or split a taxi (¥40 for the car) the last 12 km to Mutianyu. Ignore the men shouting "Great Wall! Great Wall!" at the bus door — they will quote ¥400.</t>
         </is>
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>UNESCO</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="G37" s="10" t="n">
-        <v>1890</v>
+        <v>340</v>
       </c>
     </row>
     <row r="38" ht="42" customHeight="1">
@@ -1846,21 +1863,21 @@
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>09:30  Hike Tower 14 → 20 → 23, the "Heavenly Ladder"</t>
+          <t>08:45  Mutianyu Great Wall — ticket + cable car up</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>Turn LEFT (west) at the top — the crowds all turn right. Towers 14→20 is a gorgeous rolling walk. Between 19 and 20 the Wall rears up into a near-vertical 45° staircase; past Tower 20 the restoration stops and you can see the raw, crumbling wild wall running off toward Jiankou. Two hours return, and the single best ninety minutes of the trip.</t>
+          <t>Mutianyu over Badaling, always: 2,250 m of fully restored Ming wall, 22 watchtowers, forested mountains on both sides, and a third of the crowd. Entry ¥45, shuttle ¥15, cable car ¥100 one-way. Take the cable car UP to Watchtower 14 and save your legs for the ridgeline.</t>
         </is>
       </c>
       <c r="F38" s="15" t="inlineStr">
         <is>
-          <t>Adventure</t>
+          <t>UNESCO</t>
         </is>
       </c>
       <c r="G38" s="16" t="n">
-        <v>0</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="39" ht="42" customHeight="1">
@@ -1879,17 +1896,17 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>12:15  Toboggan back down</t>
+          <t>09:30  Hike Tower 14 → 20 → 23, the "Heavenly Ladder"</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>A 1,580 m stainless-steel luge from Tower 6 to the base, ¥120. You control the brake. It is unapologetically silly and you will grin the entire way. Do not get stuck behind a nervous rider — leave a gap at the top.</t>
+          <t>Turn LEFT (west) at the top — the crowds all turn right. Towers 14→20 is a gorgeous rolling walk. Between 19 and 20 the Wall rears up into a near-vertical 45° staircase; past Tower 20 the restoration stops and you can see the raw, crumbling wild wall running off toward Jiankou. Two hours return, and the single best ninety minutes of the trip.</t>
         </is>
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>Fun</t>
+          <t>Adventure</t>
         </is>
       </c>
       <c r="G39" s="10" t="n">
@@ -1912,21 +1929,21 @@
       </c>
       <c r="D40" s="13" t="inlineStr">
         <is>
-          <t>13:00  Lunch in Mutianyu village</t>
+          <t>12:15  Toboggan back down</t>
         </is>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>The farmhouse restaurants at the base do a proper nongjia meal — trout from the mountain stream, stir-fried wild greens, hand-rolled noodles, ¥60–80 a head. Xiaolongfeng or The Schoolhouse (pricier, run by an American, excellent).</t>
+          <t>A 1,580 m stainless-steel luge from Tower 6 to the base, included in the ticket you already bought. You control the brake. It is unapologetically silly and you will grin the entire way. Do not get stuck behind a nervous rider — leave a gap at the top.</t>
         </is>
       </c>
       <c r="F40" s="15" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Fun</t>
         </is>
       </c>
       <c r="G40" s="16" t="n">
-        <v>780</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" ht="42" customHeight="1">
@@ -1945,21 +1962,21 @@
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>14:30  Return to Beijing</t>
+          <t>13:00  Lunch in Mutianyu village</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>Reverse the 916 Express. Back at Dongzhimen by about 16:30. Nap on the bus.</t>
+          <t>The farmhouse restaurants at the base do a proper nongjia meal — trout from the mountain stream, stir-fried wild greens, hand-rolled noodles, ¥60–80 a head. Xiaolongfeng, or The Schoolhouse if you want a pricier, excellent sit-down.</t>
         </is>
       </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="G41" s="10" t="n">
-        <v>340</v>
+        <v>780</v>
       </c>
     </row>
     <row r="42" ht="42" customHeight="1">
@@ -1978,21 +1995,21 @@
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>17:00  798 Art Zone</t>
+          <t>14:30  Return to Beijing</t>
         </is>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>A decommissioned 1950s East-German-built electronics factory turned into China’s biggest contemporary art district — Bauhaus sawtooth roofs, Mao-era slogans still stencilled on the girders, and 400 galleries underneath them. Free to wander; UCCA charges ¥60 if a show grabs you. Best coffee in Beijing is here too.</t>
+          <t>Reverse the 916 Express. Back at Dongzhimen by about 16:30. Sleep on the bus — you have a night train ahead and it is not the restful kind.</t>
         </is>
       </c>
       <c r="F42" s="15" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="G42" s="16" t="n">
-        <v>0</v>
+        <v>340</v>
       </c>
     </row>
     <row r="43" ht="42" customHeight="1">
@@ -2011,21 +2028,21 @@
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>19:00  Dinner near Beijing Railway Station</t>
+          <t>17:00  Collect the bag, shower, regroup</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>Collect the big bag, then eat before you board — the train dining car is grim. Grab a proper meal plus supplies for the sleeper: instant noodles (every carriage has a boiling-water tap), fruit, water, a beer.</t>
+          <t>Back to the hotel for the big bag. Most will let you use a day-use bathroom for ¥30 even after checkout — take it. Eleven hours in a sleeper compartment is much better begun clean.</t>
         </is>
       </c>
       <c r="F43" s="9" t="inlineStr">
         <is>
-          <t>Refuel</t>
+          <t>Practical</t>
         </is>
       </c>
       <c r="G43" s="10" t="n">
-        <v>420</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" ht="42" customHeight="1">
@@ -2044,21 +2061,21 @@
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>20:37  Board Z19 — overnight soft sleeper to Xi’an</t>
+          <t>18:30  Dinner near Beijing Railway Station</t>
         </is>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>Four berths per lockable compartment, clean bedding, a door that shuts. Departs Beijing West 20:37, arrives Xi’an 08:30 — eleven hours and fifty minutes that cost you a hotel night AND a travel day. ¥310 soft sleeper. Book on Trip.com 15+ days out; take a lower berth if you can, the upper has no headroom.</t>
+          <t>Eat properly before you board — the dining car is grim. Then stock the sleeper: instant noodles (every carriage has a boiling-water tap), fruit, water, a beer.</t>
         </is>
       </c>
       <c r="F44" s="15" t="inlineStr">
         <is>
-          <t>Sleep saver</t>
+          <t>Refuel</t>
         </is>
       </c>
       <c r="G44" s="16" t="n">
-        <v>3660</v>
+        <v>420</v>
       </c>
     </row>
     <row r="45" ht="42" customHeight="1">
@@ -2077,84 +2094,84 @@
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
+          <t>20:37  Board Z19 — overnight soft sleeper to Xi’an</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>Four berths per lockable compartment, clean bedding, a door that shuts. Departs 20:37, arrives Xi’an 08:30 — eleven hours and fifty minutes that cost you a hotel night AND a travel day. ¥310 soft sleeper. Book on Trip.com 15+ days out; take a lower berth if you can, the upper has no headroom.</t>
+        </is>
+      </c>
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>Sleep saver</t>
+        </is>
+      </c>
+      <c r="G45" s="10" t="n">
+        <v>3660</v>
+      </c>
+    </row>
+    <row r="46" ht="42" customHeight="1">
+      <c r="A46" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>Day 3</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="D46" s="13" t="inlineStr">
+        <is>
           <t>22:00  Lights out at 22:00 sharp</t>
         </is>
       </c>
-      <c r="E45" s="8" t="inlineStr">
+      <c r="E46" s="14" t="inlineStr">
         <is>
           <t>Chinese sleeper carriages kill the lights on the dot. Bring an eye mask and earplugs, keep your passport and phone in the pillowcase, and let 1,200 km of North China slide past in the dark.</t>
         </is>
       </c>
-      <c r="F45" s="9" t="inlineStr">
+      <c r="F46" s="15" t="inlineStr">
         <is>
           <t>Sleep</t>
         </is>
       </c>
-      <c r="G45" s="10" t="n">
+      <c r="G46" s="16" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="17" t="inlineStr"/>
-      <c r="B46" s="17" t="inlineStr"/>
-      <c r="C46" s="17" t="inlineStr"/>
-      <c r="D46" s="18" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="17" t="inlineStr"/>
+      <c r="B47" s="17" t="inlineStr"/>
+      <c r="C47" s="17" t="inlineStr"/>
+      <c r="D47" s="18" t="inlineStr">
         <is>
           <t>Day 3 — activities subtotal</t>
         </is>
       </c>
-      <c r="E46" s="19" t="inlineStr">
+      <c r="E47" s="19" t="inlineStr">
         <is>
           <t>Hotel that night: Overnight soft-sleeper train Z19 — no hotel bill tonight</t>
         </is>
       </c>
-      <c r="F46" s="19" t="inlineStr">
+      <c r="F47" s="19" t="inlineStr">
         <is>
           <t>no hotel bill</t>
         </is>
       </c>
-      <c r="G46" s="20" t="n">
+      <c r="G47" s="20" t="n">
         <v>7430</v>
       </c>
     </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="4" t="inlineStr">
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>DAY 4  ·  Eight Thousand Soldiers, One City Wall  —  Terracotta Army → golden-hour cycle on the ramparts → Muslim Quarter food crawl</t>
         </is>
-      </c>
-    </row>
-    <row r="49" ht="42" customHeight="1">
-      <c r="A49" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>Day 4</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>Xi'an</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>08:30  Arrive Xi’an, drop bags</t>
-        </is>
-      </c>
-      <c r="E49" s="8" t="inlineStr">
-        <is>
-          <t>Metro Line 4 from the station, or a ¥20 Didi to a hotel inside the City Wall. Rooms will not be ready — leave the bags, take a shower if they offer a day-use bathroom (many do for ¥30, and after a night train it is the best ₹350 of the trip).</t>
-        </is>
-      </c>
-      <c r="F49" s="9" t="inlineStr">
-        <is>
-          <t>Logistics</t>
-        </is>
-      </c>
-      <c r="G49" s="10" t="n">
-        <v>240</v>
       </c>
     </row>
     <row r="50" ht="42" customHeight="1">
@@ -2173,21 +2190,21 @@
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>09:00  Breakfast in the Muslim Quarter</t>
+          <t>08:30  Arrive Xi’an, drop bags</t>
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t>Roujiamo — the "Chinese hamburger", 2,000 years older than the other kind: slow-braised cumin lamb chopped with green chilli and stuffed into a griddled flatbread, ¥12. Chase it with hulatang, a peppery, thick beef-and-vegetable breakfast stew. The Hui Muslim community has been cooking here for 1,300 years.</t>
+          <t>Metro Line 4 from the station, or a ¥20 Didi to a hotel inside the City Wall. Rooms will not be ready — leave the bags, take a shower if they offer a day-use bathroom (many do for ¥30, and after a night train it is the best ₹350 of the trip).</t>
         </is>
       </c>
       <c r="F50" s="15" t="inlineStr">
         <is>
-          <t>Must-eat</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="G50" s="16" t="n">
-        <v>320</v>
+        <v>240</v>
       </c>
     </row>
     <row r="51" ht="42" customHeight="1">
@@ -2206,21 +2223,21 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>10:00  Tourist Bus 5 (306) to the Terracotta Army</t>
+          <t>09:00  Breakfast in the Muslim Quarter</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>From the east square of Xi’an Railway Station. ¥7, one hour, government-run — the green-and-white bus with the official number board. Ignore every private tout on that plaza; the scams here are the most persistent in China.</t>
+          <t>Roujiamo — the "Chinese hamburger", 2,000 years older than the other kind: slow-braised cumin lamb chopped with green chilli and stuffed into a griddled flatbread, ¥12. Chase it with hulatang, a peppery, thick beef-and-vegetable breakfast stew. The Hui Muslim community has been cooking here for 1,300 years.</t>
         </is>
       </c>
       <c r="F51" s="9" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Must-eat</t>
         </is>
       </c>
       <c r="G51" s="10" t="n">
-        <v>90</v>
+        <v>320</v>
       </c>
     </row>
     <row r="52" ht="42" customHeight="1">
@@ -2239,21 +2256,21 @@
       </c>
       <c r="D52" s="13" t="inlineStr">
         <is>
-          <t>11:15  Museum of the Terracotta Army</t>
+          <t>10:00  Tourist Bus 5 (306) to the Terracotta Army</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>¥120. Discovered in 1974 by farmers digging a well; over 8,000 soldiers, 130 chariots and 670 horses buried in 210 BC to guard Qin Shi Huang in the afterlife. Do the pits in reverse order — Pit 3 (the command post, small, intact), Pit 2 (the kneeling archer, the excavation still in progress under dust sheets), then Pit 1 last, so the big reveal lands at the end. Finish at the Bronze Chariots hall: two half-scale carriages of 3,400 cast parts, the finest bronzes ever recovered from China.</t>
+          <t>From the east square of Xi’an Railway Station. ¥7, one hour, government-run — the green-and-white bus with the official number board. Ignore every private tout on that plaza; the scams here are the most persistent in China.</t>
         </is>
       </c>
       <c r="F52" s="15" t="inlineStr">
         <is>
-          <t>UNESCO</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="G52" s="16" t="n">
-        <v>1420</v>
+        <v>90</v>
       </c>
     </row>
     <row r="53" ht="42" customHeight="1">
@@ -2272,21 +2289,21 @@
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>11:20  Get a guide — share the cost</t>
+          <t>11:15  Museum of the Terracotta Army</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>Licensed English guides wait at the entrance for ¥150–200 for the full site. Split four ways with other travellers in the queue it is ₹500 a head, and without one the pits are just impressive holes. They will show you the four surviving traces of original pigment and the one kneeling archer that was found unbroken.</t>
+          <t>¥120. Discovered in 1974 by farmers digging a well; over 8,000 soldiers, 130 chariots and 670 horses buried in 210 BC to guard Qin Shi Huang in the afterlife. Do the pits in reverse order — Pit 3 (the command post, small, intact), Pit 2 (the kneeling archer, the excavation still in progress under dust sheets), then Pit 1 last, so the big reveal lands at the end. Finish at the Bronze Chariots hall: two half-scale carriages of 3,400 cast parts, the finest bronzes ever recovered from China.</t>
         </is>
       </c>
       <c r="F53" s="9" t="inlineStr">
         <is>
-          <t>Worth it</t>
+          <t>UNESCO</t>
         </is>
       </c>
       <c r="G53" s="10" t="n">
-        <v>500</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="54" ht="42" customHeight="1">
@@ -2305,21 +2322,21 @@
       </c>
       <c r="D54" s="13" t="inlineStr">
         <is>
-          <t>14:45  Back to the city</t>
+          <t>11:20  Get a guide — share the cost</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>Same bus, one hour. Eat the persimmon cakes you bought at breakfast on the way.</t>
+          <t>Licensed English guides wait at the entrance for ¥150–200 for the full site. Split four ways with other travellers in the queue it is ₹500 a head, and without one the pits are just impressive holes. They will show you the four surviving traces of original pigment and the one kneeling archer that was found unbroken.</t>
         </is>
       </c>
       <c r="F54" s="15" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Worth it</t>
         </is>
       </c>
       <c r="G54" s="16" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
     </row>
     <row r="55" ht="42" customHeight="1">
@@ -2338,21 +2355,21 @@
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>16:15  Cycle the Xi’an City Wall at golden hour</t>
+          <t>14:45  Back to the city</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>The single best thing you will do in Xi’an. 13.7 km of complete, unbroken Ming rampart — 12 m high, 15 m wide on top, the most intact ancient city wall on earth. Entry ¥54, bike hire ¥45 for 3 hours (tandem ¥90). A full lap takes 100 minutes at a lazy pace. Start at the South Gate, ride anticlockwise, and time it so the last stretch is at sunset: old grey-tiled courtyards inside the wall on your right, glass towers outside on your left, 600 years apart and 20 metres from each other.</t>
+          <t>Same bus, one hour. Eat the persimmon cakes you bought at breakfast on the way.</t>
         </is>
       </c>
       <c r="F55" s="9" t="inlineStr">
         <is>
-          <t>Unmissable</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="G55" s="10" t="n">
-        <v>1170</v>
+        <v>90</v>
       </c>
     </row>
     <row r="56" ht="42" customHeight="1">
@@ -2371,21 +2388,21 @@
       </c>
       <c r="D56" s="13" t="inlineStr">
         <is>
-          <t>18:45  Muslim Quarter food crawl — the real dinner</t>
+          <t>16:15  Cycle the Xi’an City Wall at golden hour</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>Do not sit down for a meal. Graze Beiyuanmen street end to end: yangrou paomo (you tear the flatbread into your own bowl, they pour the mutton broth over — ¥35), biang biang noodles (belt-wide, hand-slapped, chilli-oil-doused, and written with the most complex character in Chinese, 58 strokes), lamb kebabs over charcoal, rou jia mo again because you want to, crystal persimmon cakes, and hot pomegranate juice. Budget ₹700 and arrive hungry.</t>
+          <t>The single best thing you will do in Xi’an. 13.7 km of complete, unbroken Ming rampart — 12 m high, 15 m wide on top, the most intact ancient city wall on earth. Entry ¥54, bike hire ¥45 for 3 hours (tandem ¥90). A full lap takes 100 minutes at a lazy pace. Start at the South Gate, ride anticlockwise, and time it so the last stretch is at sunset: old grey-tiled courtyards inside the wall on your right, glass towers outside on your left, 600 years apart and 20 metres from each other.</t>
         </is>
       </c>
       <c r="F56" s="15" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Unmissable</t>
         </is>
       </c>
       <c r="G56" s="16" t="n">
-        <v>780</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="57" ht="42" customHeight="1">
@@ -2404,21 +2421,21 @@
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>20:30  Bell Tower &amp; Drum Tower lit up</t>
+          <t>18:45  Muslim Quarter food crawl — the real dinner</t>
         </is>
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>The two Ming towers sit floodlit in the middle of the city’s biggest roundabout, and the underground pedestrian passage puts you right beneath them. Fifteen minutes, no ticket needed for the outside view, and Xi’an’s best night photograph.</t>
+          <t>Do not sit down for a meal. Graze Beiyuanmen street end to end: yangrou paomo (you tear the flatbread into your own bowl, they pour the mutton broth over — ¥35), biang biang noodles (belt-wide, hand-slapped, chilli-oil-doused, and written with the most complex character in Chinese, 58 strokes), lamb kebabs over charcoal, rou jia mo again because you want to, crystal persimmon cakes, and hot pomegranate juice. Budget ₹700 and arrive hungry.</t>
         </is>
       </c>
       <c r="F57" s="9" t="inlineStr">
         <is>
-          <t>Photo</t>
+          <t>Legendary</t>
         </is>
       </c>
       <c r="G57" s="10" t="n">
-        <v>0</v>
+        <v>780</v>
       </c>
     </row>
     <row r="58" ht="42" customHeight="1">
@@ -2437,21 +2454,21 @@
       </c>
       <c r="D58" s="13" t="inlineStr">
         <is>
-          <t>21:00  Big Wild Goose Pagoda fountain show</t>
+          <t>20:30  Bell Tower &amp; Drum Tower lit up</t>
         </is>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>Asia’s largest musical fountain erupts in the North Square at 21:00 (20:30 in winter), free, in front of the 652 AD pagoda that Xuanzang built to house the sutras he carried back from India. There is a nice symmetry in an Indian traveller watching that particular building.</t>
+          <t>The two Ming towers sit floodlit in the middle of the city’s biggest roundabout, and the underground pedestrian passage puts you right beneath them. Fifteen minutes, no ticket needed for the outside view, and Xi’an’s best night photograph.</t>
         </is>
       </c>
       <c r="F58" s="15" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Photo</t>
         </is>
       </c>
       <c r="G58" s="16" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" ht="42" customHeight="1">
@@ -2470,84 +2487,84 @@
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
+          <t>21:00  Big Wild Goose Pagoda fountain show</t>
+        </is>
+      </c>
+      <c r="E59" s="8" t="inlineStr">
+        <is>
+          <t>Asia’s largest musical fountain erupts in the North Square at 21:00 (20:30 in winter), free, in front of the 652 AD pagoda that Xuanzang built to house the sutras he carried back from India. There is a nice symmetry in an Indian traveller watching that particular building.</t>
+        </is>
+      </c>
+      <c r="F59" s="9" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="G59" s="10" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" ht="42" customHeight="1">
+      <c r="A60" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B60" s="12" t="inlineStr">
+        <is>
+          <t>Day 4</t>
+        </is>
+      </c>
+      <c r="C60" s="12" t="inlineStr">
+        <is>
+          <t>Xi'an</t>
+        </is>
+      </c>
+      <c r="D60" s="13" t="inlineStr">
+        <is>
           <t>22:15  Hotel, finally a proper bed</t>
         </is>
       </c>
-      <c r="E59" s="8" t="inlineStr">
+      <c r="E60" s="14" t="inlineStr">
         <is>
           <t>Inside the walls, near the Bell Tower. ₹2,300 gets you a genuinely good boutique room here — Xi’an is the best-value city of the three.</t>
         </is>
       </c>
-      <c r="F59" s="9" t="inlineStr">
+      <c r="F60" s="15" t="inlineStr">
         <is>
           <t>Stay</t>
         </is>
       </c>
-      <c r="G59" s="10" t="n">
+      <c r="G60" s="16" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="17" t="inlineStr"/>
-      <c r="B60" s="17" t="inlineStr"/>
-      <c r="C60" s="17" t="inlineStr"/>
-      <c r="D60" s="18" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="17" t="inlineStr"/>
+      <c r="B61" s="17" t="inlineStr"/>
+      <c r="C61" s="17" t="inlineStr"/>
+      <c r="D61" s="18" t="inlineStr">
         <is>
           <t>Day 4 — activities subtotal</t>
         </is>
       </c>
-      <c r="E60" s="19" t="inlineStr">
+      <c r="E61" s="19" t="inlineStr">
         <is>
           <t>Hotel that night: Boutique hotel inside the City Wall, near the Bell Tower</t>
         </is>
       </c>
-      <c r="F60" s="19" t="inlineStr">
+      <c r="F61" s="19" t="inlineStr">
         <is>
           <t>Stay ₹2,300</t>
         </is>
       </c>
-      <c r="G60" s="20" t="n">
+      <c r="G61" s="20" t="n">
         <v>4710</v>
       </c>
     </row>
-    <row r="62" ht="22" customHeight="1">
-      <c r="A62" s="4" t="inlineStr">
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
         <is>
           <t>DAY 5  ·  Dawn Mosque, 350 km/h, Neon Riverfront  —  Great Mosque of Xi’an → bullet train east → The Bund switches on</t>
         </is>
-      </c>
-    </row>
-    <row r="63" ht="42" customHeight="1">
-      <c r="A63" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>Day 5</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>Shanghai</t>
-        </is>
-      </c>
-      <c r="D63" s="7" t="inlineStr">
-        <is>
-          <t>07:00  Great Mosque of Xi’an</t>
-        </is>
-      </c>
-      <c r="E63" s="8" t="inlineStr">
-        <is>
-          <t>¥25, and almost nobody goes. Founded in 742 AD, it looks nothing like a mosque anywhere else on earth — no dome, no minaret, just five courtyards of Chinese timber pavilions, moon gates and a pagoda that serves as the minaret, with Arabic calligraphy carved into Ming woodwork. Empty and silent at 07:00. Forty minutes well spent.</t>
-        </is>
-      </c>
-      <c r="F63" s="9" t="inlineStr">
-        <is>
-          <t>Hidden gem</t>
-        </is>
-      </c>
-      <c r="G63" s="10" t="n">
-        <v>300</v>
       </c>
     </row>
     <row r="64" ht="42" customHeight="1">
@@ -2566,21 +2583,21 @@
       </c>
       <c r="D64" s="13" t="inlineStr">
         <is>
-          <t>08:15  Beiyuanmen morning market</t>
+          <t>07:00  Great Mosque of Xi’an</t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>The same street as last night, transformed: no tourists, just butchers, bread ovens and men drinking tea. Buy breakfast — a sesame flatbread straight off the oven wall, ¥5.</t>
+          <t>¥25, and almost nobody goes. Founded in 742 AD, it looks nothing like a mosque anywhere else on earth — no dome, no minaret, just five courtyards of Chinese timber pavilions, moon gates and a pagoda that serves as the minaret, with Arabic calligraphy carved into Ming woodwork. Empty and silent at 07:00. Forty minutes well spent.</t>
         </is>
       </c>
       <c r="F64" s="15" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Hidden gem</t>
         </is>
       </c>
       <c r="G64" s="16" t="n">
-        <v>120</v>
+        <v>300</v>
       </c>
     </row>
     <row r="65" ht="42" customHeight="1">
@@ -2599,21 +2616,21 @@
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>09:10  Xi'an North → Shanghai Hongqiao, G-series high-speed</t>
+          <t>08:15  Beiyuanmen morning market</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>Metro Line 2 to Xi’an North (25 min — leave the hotel by 08:15). Train G1974 or similar: 1,400 km in 6 hours at 350 km/h, second class ¥515. Reserve a window seat on the A or F side, buy a lunchbox from the trolley (¥45), and watch the Loess Plateau turn into the Yangtze delta. Cheaper and less hassle than flying once you count airport transfers.</t>
+          <t>The same street as last night, transformed: no tourists, just butchers, bread ovens and men drinking tea. Buy breakfast — a sesame flatbread straight off the oven wall, ¥5.</t>
         </is>
       </c>
       <c r="F65" s="9" t="inlineStr">
         <is>
-          <t>Big move</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="G65" s="10" t="n">
-        <v>6080</v>
+        <v>120</v>
       </c>
     </row>
     <row r="66" ht="42" customHeight="1">
@@ -2632,21 +2649,21 @@
       </c>
       <c r="D66" s="13" t="inlineStr">
         <is>
-          <t>15:30  Arrive Hongqiao → Metro Line 2 to the hotel</t>
+          <t>09:10  Xi'an North → Shanghai Hongqiao, G-series high-speed</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>Line 2 runs from inside the station straight to People’s Square / Jing’an. ¥5, 35 min. Shanghai’s metro is the largest in the world — 831 km of it — and you can do this entire city on it.</t>
+          <t>Metro Line 2 to Xi’an North (25 min — leave the hotel by 08:15). Train G1974 or similar: 1,400 km in 6 hours at 350 km/h, second class ¥515. Reserve a window seat on the A or F side, buy a lunchbox from the trolley (¥45), and watch the Loess Plateau turn into the Yangtze delta. Cheaper and less hassle than flying once you count airport transfers.</t>
         </is>
       </c>
       <c r="F66" s="15" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Big move</t>
         </is>
       </c>
       <c r="G66" s="16" t="n">
-        <v>60</v>
+        <v>6080</v>
       </c>
     </row>
     <row r="67" ht="42" customHeight="1">
@@ -2665,21 +2682,21 @@
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>16:30  Check in, shower, change</t>
+          <t>15:30  Arrive Hongqiao → Metro Line 2 to the hotel</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>Jing'an or People's Square. Central, safe, walkable to the Bund in 20 minutes, and two metro lines under your feet.</t>
+          <t>Line 2 runs from inside the station straight to People’s Square / Jing’an. ¥5, 35 min. Shanghai’s metro is the largest in the world — 831 km of it — and you can do this entire city on it.</t>
         </is>
       </c>
       <c r="F67" s="9" t="inlineStr">
         <is>
-          <t>Stay</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="G67" s="10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="68" ht="42" customHeight="1">
@@ -2698,17 +2715,17 @@
       </c>
       <c r="D68" s="13" t="inlineStr">
         <is>
-          <t>18:00  The Bund — arrive before the lights</t>
+          <t>16:30  Check in, shower, change</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>Walk the 1.5 km promenade from Waibaidu Bridge south. On your right, 52 surviving 1920s buildings — neoclassical banks, art-deco hotels, the whole colonial waterfront of the "Paris of the East". On your left, across 600 m of Huangpu river, the Pudong skyline: the Oriental Pearl, the bottle-opener SWFC, and the twisting 632 m Shanghai Tower. Be there by 18:15. Nothing else in Asia does this.</t>
+          <t>Jing'an or People's Square. Central, safe, walkable to the Bund in 20 minutes, and two metro lines under your feet.</t>
         </is>
       </c>
       <c r="F68" s="15" t="inlineStr">
         <is>
-          <t>Iconic</t>
+          <t>Stay</t>
         </is>
       </c>
       <c r="G68" s="16" t="n">
@@ -2731,21 +2748,21 @@
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>19:30  Dinner: xiaolongbao done properly</t>
+          <t>18:00  The Bund — arrive before the lights</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>Jia Jia Tang Bao for the local, no-frills version (¥30, queue out the door, cash-and-carry energy) or Din Tai Fung for the polished 18-fold benchmark (¥120). The technique: nip the top, sip the soup out first, then dip in black vinegar with ginger. Bite it whole and you will burn your mouth and lose the broth — everyone does it once.</t>
+          <t>Walk the 1.5 km promenade from Waibaidu Bridge south. On your right, 52 surviving 1920s buildings — neoclassical banks, art-deco hotels, the whole colonial waterfront of the "Paris of the East". On your left, across 600 m of Huangpu river, the Pudong skyline: the Oriental Pearl, the bottle-opener SWFC, and the twisting 632 m Shanghai Tower. Be there by 18:15. Nothing else in Asia does this.</t>
         </is>
       </c>
       <c r="F69" s="9" t="inlineStr">
         <is>
-          <t>Must-eat</t>
+          <t>Iconic</t>
         </is>
       </c>
       <c r="G69" s="10" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" ht="42" customHeight="1">
@@ -2764,21 +2781,21 @@
       </c>
       <c r="D70" s="13" t="inlineStr">
         <is>
-          <t>21:00  Huangpu River night cruise</t>
+          <t>19:30  Dinner: xiaolongbao done properly</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>¥120 for 50 minutes from the Bund pier. You get both banks lit at once and the only angle where the Bund’s 1920s skyline and Pudong’s 2020s one sit in the same frame. Buy the ticket at the pier, not from a tout, and stand at the bow on the upper deck.</t>
+          <t>Jia Jia Tang Bao for the local, no-frills version (¥30, queue out the door, cash-and-carry energy) or Din Tai Fung for the polished 18-fold benchmark (¥120). The technique: nip the top, sip the soup out first, then dip in black vinegar with ginger. Bite it whole and you will burn your mouth and lose the broth — everyone does it once.</t>
         </is>
       </c>
       <c r="F70" s="15" t="inlineStr">
         <is>
-          <t>Splurge</t>
+          <t>Must-eat</t>
         </is>
       </c>
       <c r="G70" s="16" t="n">
-        <v>1180</v>
+        <v>900</v>
       </c>
     </row>
     <row r="71" ht="42" customHeight="1">
@@ -2797,84 +2814,84 @@
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
+          <t>21:00  Huangpu River night cruise</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>¥120 for 50 minutes from the Bund pier. You get both banks lit at once and the only angle where the Bund’s 1920s skyline and Pudong’s 2020s one sit in the same frame. Buy the ticket at the pier, not from a tout, and stand at the bow on the upper deck.</t>
+        </is>
+      </c>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>Splurge</t>
+        </is>
+      </c>
+      <c r="G71" s="10" t="n">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="72" ht="42" customHeight="1">
+      <c r="A72" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B72" s="12" t="inlineStr">
+        <is>
+          <t>Day 5</t>
+        </is>
+      </c>
+      <c r="C72" s="12" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
+      <c r="D72" s="13" t="inlineStr">
+        <is>
           <t>22:15  Nightcap on Nanjing East Road</t>
         </is>
       </c>
-      <c r="E71" s="8" t="inlineStr">
+      <c r="E72" s="14" t="inlineStr">
         <is>
           <t>Walk back through the pedestrian strip — all lights, trams and crowds until midnight. Or a ¥60 cocktail at a Bund rooftop if the budget tracker is looking kind.</t>
         </is>
       </c>
-      <c r="F71" s="9" t="inlineStr">
+      <c r="F72" s="15" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="G71" s="10" t="n">
+      <c r="G72" s="16" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="17" t="inlineStr"/>
-      <c r="B72" s="17" t="inlineStr"/>
-      <c r="C72" s="17" t="inlineStr"/>
-      <c r="D72" s="18" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="17" t="inlineStr"/>
+      <c r="B73" s="17" t="inlineStr"/>
+      <c r="C73" s="17" t="inlineStr"/>
+      <c r="D73" s="18" t="inlineStr">
         <is>
           <t>Day 5 — activities subtotal</t>
         </is>
       </c>
-      <c r="E72" s="19" t="inlineStr">
+      <c r="E73" s="19" t="inlineStr">
         <is>
           <t>Hotel that night: Jing'an / People's Square 3★</t>
         </is>
       </c>
-      <c r="F72" s="19" t="inlineStr">
+      <c r="F73" s="19" t="inlineStr">
         <is>
           <t>Stay ₹3,100</t>
         </is>
       </c>
-      <c r="G72" s="20" t="n">
+      <c r="G73" s="20" t="n">
         <v>8640</v>
       </c>
     </row>
-    <row r="74" ht="22" customHeight="1">
-      <c r="A74" s="4" t="inlineStr">
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="4" t="inlineStr">
         <is>
           <t>DAY 6  ·  Water Town, Old Gardens, and the 118th Floor  —  Zhujiajiao canals → Yu Garden → Tianzifang lanes → sunset from Shanghai Tower</t>
         </is>
-      </c>
-    </row>
-    <row r="75" ht="42" customHeight="1">
-      <c r="A75" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>Day 6</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>Shanghai</t>
-        </is>
-      </c>
-      <c r="D75" s="7" t="inlineStr">
-        <is>
-          <t>07:00  Breakfast: Yang's Fry Dumplings</t>
-        </is>
-      </c>
-      <c r="E75" s="8" t="inlineStr">
-        <is>
-          <t>Shengjianbao — pork buns pan-fried until the bottoms are lacquered mahogany, the tops soft, the insides full of scalding soup, finished with sesame and spring onion. Four for ¥8. Shanghai’s single best breakfast and it costs ₹95.</t>
-        </is>
-      </c>
-      <c r="F75" s="9" t="inlineStr">
-        <is>
-          <t>Must-eat</t>
-        </is>
-      </c>
-      <c r="G75" s="10" t="n">
-        <v>160</v>
       </c>
     </row>
     <row r="76" ht="42" customHeight="1">
@@ -2893,21 +2910,21 @@
       </c>
       <c r="D76" s="13" t="inlineStr">
         <is>
-          <t>08:00  Metro Line 17 to Zhujiajiao</t>
+          <t>07:00  Breakfast: Yang's Fry Dumplings</t>
         </is>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t>¥7, about an hour from Hongqiao. Get on at the front of the train and out at Zhujiajiao station, then a 10-minute walk or the ¥1 shuttle to the old town. Going early is the whole trick — by 11:00 the day-tour coaches from the city arrive and it becomes a different, worse place.</t>
+          <t>Shengjianbao — pork buns pan-fried until the bottoms are lacquered mahogany, the tops soft, the insides full of scalding soup, finished with sesame and spring onion. Four for ¥8. Shanghai’s single best breakfast and it costs ₹95.</t>
         </is>
       </c>
       <c r="F76" s="15" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Must-eat</t>
         </is>
       </c>
       <c r="G76" s="16" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
     </row>
     <row r="77" ht="42" customHeight="1">
@@ -2926,21 +2943,21 @@
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>09:15  Zhujiajiao ancient water town</t>
+          <t>08:00  Metro Line 17 to Zhujiajiao</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>A 1,700-year-old canal settlement on the edge of Shanghai: 36 stone bridges, whitewashed Ming and Qing houses standing directly in the water, laundry on poles over the canals. Walk to the five-arched Fangsheng Bridge (1571), duck into Kezhi Garden (¥30), then take a wooden rowing boat — ¥120 for the boat, split it, 20 minutes, and it is the only way to see the town from the height it was built for.</t>
+          <t>¥7, about an hour from Hongqiao. Get on at the front of the train and out at Zhujiajiao station, then a 10-minute walk or the ¥1 shuttle to the old town. Going early is the whole trick — by 11:00 the day-tour coaches from the city arrive and it becomes a different, worse place.</t>
         </is>
       </c>
       <c r="F77" s="9" t="inlineStr">
         <is>
-          <t>Day trip</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="G77" s="10" t="n">
-        <v>620</v>
+        <v>180</v>
       </c>
     </row>
     <row r="78" ht="42" customHeight="1">
@@ -2959,21 +2976,21 @@
       </c>
       <c r="D78" s="13" t="inlineStr">
         <is>
-          <t>12:30  Back into the city</t>
+          <t>09:15  Zhujiajiao ancient water town</t>
         </is>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>Line 17 → Line 2 → Line 10 to Yuyuan Garden station. About 75 minutes; eat a zongzi on the train.</t>
+          <t>A 1,700-year-old canal settlement on the edge of Shanghai: 36 stone bridges, whitewashed Ming and Qing houses standing directly in the water, laundry on poles over the canals. Walk to the five-arched Fangsheng Bridge (1571), duck into Kezhi Garden (¥30), then take a wooden rowing boat — ¥120 for the boat, split it, 20 minutes, and it is the only way to see the town from the height it was built for.</t>
         </is>
       </c>
       <c r="F78" s="15" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Day trip</t>
         </is>
       </c>
       <c r="G78" s="16" t="n">
-        <v>90</v>
+        <v>620</v>
       </c>
     </row>
     <row r="79" ht="42" customHeight="1">
@@ -2992,21 +3009,21 @@
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>14:00  Yu Garden &amp; the Old City bazaar</t>
+          <t>12:30  Back into the city</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>¥40. A Ming scholar-official’s private garden from 1559, two acres of deliberately disorienting rockeries, dragon-topped walls, carp ponds and moon gates, all folded into a space you can cross in 90 seconds — the point is that you never can. Outside it, the Yuyuan Bazaar is loud, fake-antique and fun; the Huxinting teahouse on its zigzag bridge (zigzagged because evil spirits can only travel in straight lines) is worth the ¥60 pot.</t>
+          <t>Line 17 → Line 2 → Line 10 to Yuyuan Garden station. About 75 minutes; eat a zongzi on the train.</t>
         </is>
       </c>
       <c r="F79" s="9" t="inlineStr">
         <is>
-          <t>Classic</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="G79" s="10" t="n">
-        <v>620</v>
+        <v>90</v>
       </c>
     </row>
     <row r="80" ht="42" customHeight="1">
@@ -3025,21 +3042,21 @@
       </c>
       <c r="D80" s="13" t="inlineStr">
         <is>
-          <t>16:00  Tianzifang</t>
+          <t>14:00  Yu Garden &amp; the Old City bazaar</t>
         </is>
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t>Free. A block of 1930s shikumen stone-gate lane houses in the French Concession, now a warren of alleys barely two metres wide packed with studios, tiny bars, ceramics and coffee. Laundry still hangs from the upper windows because people genuinely live above the shops. Get lost on purpose for an hour.</t>
+          <t>¥40. A Ming scholar-official’s private garden from 1559, two acres of deliberately disorienting rockeries, dragon-topped walls, carp ponds and moon gates, all folded into a space you can cross in 90 seconds — the point is that you never can. Outside it, the Yuyuan Bazaar is loud, fake-antique and fun; the Huxinting teahouse on its zigzag bridge (zigzagged because evil spirits can only travel in straight lines) is worth the ¥60 pot.</t>
         </is>
       </c>
       <c r="F80" s="15" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Classic</t>
         </is>
       </c>
       <c r="G80" s="16" t="n">
-        <v>240</v>
+        <v>620</v>
       </c>
     </row>
     <row r="81" ht="42" customHeight="1">
@@ -3058,21 +3075,21 @@
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>17:30  Shanghai Tower, Observation Deck 118F</t>
+          <t>16:00  Tianzifang</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>¥180, and book the 17:45–18:00 slot online days ahead — you want to go up in daylight and come down in the dark. 632 m, the second-tallest building on earth, and the lift does 118 floors in 55 seconds at 20.5 m/s. From the top the Oriental Pearl looks like a toy and the Huangpu is a silver thread. Cheaper alternative: the SWFC "bottle opener" 100F at ¥180, which has a glass floor.</t>
+          <t>Free. A block of 1930s shikumen stone-gate lane houses in the French Concession, now a warren of alleys barely two metres wide packed with studios, tiny bars, ceramics and coffee. Laundry still hangs from the upper windows because people genuinely live above the shops. Get lost on purpose for an hour.</t>
         </is>
       </c>
       <c r="F81" s="9" t="inlineStr">
         <is>
-          <t>Splurge</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="G81" s="10" t="n">
-        <v>2130</v>
+        <v>240</v>
       </c>
     </row>
     <row r="82" ht="42" customHeight="1">
@@ -3091,21 +3108,21 @@
       </c>
       <c r="D82" s="13" t="inlineStr">
         <is>
-          <t>19:30  Dinner in Xintiandi or Found158</t>
+          <t>17:30  Shanghai Tower, Observation Deck 118F</t>
         </is>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>Xintiandi is restored shikumen turned upmarket dining; Found158 is a sunken plaza of bars and kitchens off Julu Road that Shanghai’s own twenty-somethings actually use. Either way, ₹600–800 for a proper sit-down meal with a drink.</t>
+          <t>¥180, and book the 17:45–18:00 slot online days ahead — you want to go up in daylight and come down in the dark. 632 m, the second-tallest building on earth, and the lift does 118 floors in 55 seconds at 20.5 m/s. From the top the Oriental Pearl looks like a toy and the Huangpu is a silver thread. Cheaper alternative: the SWFC "bottle opener" 100F at ¥180, which has a glass floor.</t>
         </is>
       </c>
       <c r="F82" s="15" t="inlineStr">
         <is>
-          <t>Dinner</t>
+          <t>Splurge</t>
         </is>
       </c>
       <c r="G82" s="16" t="n">
-        <v>700</v>
+        <v>2130</v>
       </c>
     </row>
     <row r="83" ht="42" customHeight="1">
@@ -3124,84 +3141,84 @@
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
+          <t>19:30  Dinner in Xintiandi or Found158</t>
+        </is>
+      </c>
+      <c r="E83" s="8" t="inlineStr">
+        <is>
+          <t>Xintiandi is restored shikumen turned upmarket dining; Found158 is a sunken plaza of bars and kitchens off Julu Road that Shanghai’s own twenty-somethings actually use. Either way, ₹600–800 for a proper sit-down meal with a drink.</t>
+        </is>
+      </c>
+      <c r="F83" s="9" t="inlineStr">
+        <is>
+          <t>Dinner</t>
+        </is>
+      </c>
+      <c r="G83" s="10" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="84" ht="42" customHeight="1">
+      <c r="A84" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B84" s="12" t="inlineStr">
+        <is>
+          <t>Day 6</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
+      <c r="D84" s="13" t="inlineStr">
+        <is>
           <t>21:15  French Concession night walk</t>
         </is>
       </c>
-      <c r="E83" s="8" t="inlineStr">
+      <c r="E84" s="14" t="inlineStr">
         <is>
           <t>Wuyuan Road and Anfu Road — plane trees, art-deco villas, wine bars and the quietest, most European corner of the city. Walk it, do not metro it. Home by 23:00.</t>
         </is>
       </c>
-      <c r="F83" s="9" t="inlineStr">
+      <c r="F84" s="15" t="inlineStr">
         <is>
           <t>Chill</t>
         </is>
       </c>
-      <c r="G83" s="10" t="n">
+      <c r="G84" s="16" t="n">
         <v>140</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="17" t="inlineStr"/>
-      <c r="B84" s="17" t="inlineStr"/>
-      <c r="C84" s="17" t="inlineStr"/>
-      <c r="D84" s="18" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="17" t="inlineStr"/>
+      <c r="B85" s="17" t="inlineStr"/>
+      <c r="C85" s="17" t="inlineStr"/>
+      <c r="D85" s="18" t="inlineStr">
         <is>
           <t>Day 6 — activities subtotal</t>
         </is>
       </c>
-      <c r="E84" s="19" t="inlineStr">
+      <c r="E85" s="19" t="inlineStr">
         <is>
           <t>Hotel that night: Jing'an / People's Square 3★</t>
         </is>
       </c>
-      <c r="F84" s="19" t="inlineStr">
+      <c r="F85" s="19" t="inlineStr">
         <is>
           <t>Stay ₹3,100</t>
         </is>
       </c>
-      <c r="G84" s="20" t="n">
+      <c r="G85" s="20" t="n">
         <v>4880</v>
       </c>
     </row>
-    <row r="86" ht="22" customHeight="1">
-      <c r="A86" s="4" t="inlineStr">
+    <row r="87" ht="22" customHeight="1">
+      <c r="A87" s="4" t="inlineStr">
         <is>
           <t>DAY 7  ·  Last Bites, and 431 km/h to the Plane  —  Tai chi on the Bund → Jing’an Temple → Nanjing Road → the Maglev → home</t>
         </is>
-      </c>
-    </row>
-    <row r="87" ht="42" customHeight="1">
-      <c r="A87" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B87" s="6" t="inlineStr">
-        <is>
-          <t>Day 7</t>
-        </is>
-      </c>
-      <c r="C87" s="6" t="inlineStr">
-        <is>
-          <t>Shanghai</t>
-        </is>
-      </c>
-      <c r="D87" s="7" t="inlineStr">
-        <is>
-          <t>07:00  Sunrise on the Bund, the other version</t>
-        </is>
-      </c>
-      <c r="E87" s="8" t="inlineStr">
-        <is>
-          <t>Come back at dawn and it is a completely different place: no crowds, soft light on the 1920s facades, and dozens of Shanghainese doing tai chi, fan dancing and ballroom on the promenade. This is the Bund photograph nobody comes home with.</t>
-        </is>
-      </c>
-      <c r="F87" s="9" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="G87" s="10" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="88" ht="42" customHeight="1">
@@ -3220,21 +3237,21 @@
       </c>
       <c r="D88" s="13" t="inlineStr">
         <is>
-          <t>08:30  Breakfast: the classic Shanghai four</t>
+          <t>07:00  Sunrise on the Bund, the other version</t>
         </is>
       </c>
       <c r="E88" s="14" t="inlineStr">
         <is>
-          <t>Doujiang (warm soy milk, savoury version with dried shrimp and pickles), youtiao (fried dough stick, for dunking), cifantuan (sticky-rice roll wrapped around a crushed youtiao and pork floss) and a scallion pancake. Any corner shop, ₹150 total.</t>
+          <t>Come back at dawn and it is a completely different place: no crowds, soft light on the 1920s facades, and dozens of Shanghainese doing tai chi, fan dancing and ballroom on the promenade. This is the Bund photograph nobody comes home with.</t>
         </is>
       </c>
       <c r="F88" s="15" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="G88" s="16" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" ht="42" customHeight="1">
@@ -3253,21 +3270,21 @@
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>09:45  Jing'an Temple</t>
+          <t>08:30  Breakfast: the classic Shanghai four</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>¥50. A 1,780-year-old Buddhist temple rebuilt in gold and Burmese teak, sitting in a hollow surrounded on all four sides by glass office towers and a Prada store. The contrast is the point, and it is the most Shanghai image in Shanghai. Alternative: the Shanghai Museum East in Pudong — free, colossal, book ahead, and needs three hours you may not have.</t>
+          <t>Doujiang (warm soy milk, savoury version with dried shrimp and pickles), youtiao (fried dough stick, for dunking), cifantuan (sticky-rice roll wrapped around a crushed youtiao and pork floss) and a scallion pancake. Any corner shop, ₹150 total.</t>
         </is>
       </c>
       <c r="F89" s="9" t="inlineStr">
         <is>
-          <t>Pick one</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="G89" s="10" t="n">
-        <v>600</v>
+        <v>180</v>
       </c>
     </row>
     <row r="90" ht="42" customHeight="1">
@@ -3286,21 +3303,21 @@
       </c>
       <c r="D90" s="13" t="inlineStr">
         <is>
-          <t>11:15  Nanjing Road + the souvenir run</t>
+          <t>09:45  Jing'an Temple</t>
         </is>
       </c>
       <c r="E90" s="14" t="inlineStr">
         <is>
-          <t>What to actually buy: loose tea from a proper shop (Longjing green or a pressed pu-erh cake), a carved stone name-chop with your name in seal script (¥80, cut while you wait), silk scarves, a Jingdezhen porcelain cup. What to skip: anything sold by someone who approached you first.</t>
+          <t>¥50. A 1,780-year-old Buddhist temple rebuilt in gold and Burmese teak, sitting in a hollow surrounded on all four sides by glass office towers and a Prada store. The contrast is the point, and it is the most Shanghai image in Shanghai. Alternative: the Shanghai Museum East in Pudong — free, colossal, book ahead, and needs three hours you may not have.</t>
         </is>
       </c>
       <c r="F90" s="15" t="inlineStr">
         <is>
-          <t>Shopping</t>
+          <t>Pick one</t>
         </is>
       </c>
       <c r="G90" s="16" t="n">
-        <v>1600</v>
+        <v>600</v>
       </c>
     </row>
     <row r="91" ht="42" customHeight="1">
@@ -3319,21 +3336,21 @@
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>13:00  Last lunch: whatever you liked most</t>
+          <t>11:15  Nanjing Road + the souvenir run</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>Mine would be one more round of xiaolongbao and a bowl of scallion-oil noodles. Yours might be hotpot. Either way, eat it slowly — you are about to be on a plane for six hours.</t>
+          <t>What to actually buy: loose tea from a proper shop (Longjing green or a pressed pu-erh cake), a carved stone name-chop with your name in seal script (¥80, cut while you wait), silk scarves, a Jingdezhen porcelain cup. What to skip: anything sold by someone who approached you first.</t>
         </is>
       </c>
       <c r="F91" s="9" t="inlineStr">
         <is>
-          <t>Farewell</t>
+          <t>Shopping</t>
         </is>
       </c>
       <c r="G91" s="10" t="n">
-        <v>560</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="92" ht="42" customHeight="1">
@@ -3352,21 +3369,21 @@
       </c>
       <c r="D92" s="13" t="inlineStr">
         <is>
-          <t>14:30  Collect bags, Metro Line 2 to Longyang Road</t>
+          <t>13:00  Last lunch: whatever you liked most</t>
         </is>
       </c>
       <c r="E92" s="14" t="inlineStr">
         <is>
-          <t>Hotel checkout is usually noon; leave the bags in the morning and swing back. Line 2 to Longyang Road, ¥5, 30 minutes.</t>
+          <t>Mine would be one more round of xiaolongbao and a bowl of scallion-oil noodles. Yours might be hotpot. Either way, eat it slowly — you are about to be on a plane for six hours.</t>
         </is>
       </c>
       <c r="F92" s="15" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Farewell</t>
         </is>
       </c>
       <c r="G92" s="16" t="n">
-        <v>60</v>
+        <v>560</v>
       </c>
     </row>
     <row r="93" ht="42" customHeight="1">
@@ -3385,21 +3402,21 @@
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>15:20  The Maglev: Longyang Road → Pudong Airport</t>
+          <t>14:30  Collect bags, Metro Line 2 to Longyang Road</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>¥50 with a boarding pass (¥50 single, ¥40 with same-day air ticket). 30 km in 7 minutes 20 seconds, topping out at 431 km/h — the fastest commercial train on the planet, magnetically levitated 10 mm off the guideway. There is a speedometer in each carriage. Everybody films it. Do the 15:00–15:30 departures; they run the full-speed schedule.</t>
+          <t>Hotel checkout is usually noon; leave the bags in the morning and swing back. Line 2 to Longyang Road, ¥5, 30 minutes.</t>
         </is>
       </c>
       <c r="F93" s="9" t="inlineStr">
         <is>
-          <t>Do it</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="G93" s="10" t="n">
-        <v>590</v>
+        <v>60</v>
       </c>
     </row>
     <row r="94" ht="42" customHeight="1">
@@ -3418,21 +3435,21 @@
       </c>
       <c r="D94" s="13" t="inlineStr">
         <is>
-          <t>15:45  Pudong International (PVG), Terminal 2</t>
+          <t>15:20  The Maglev: Longyang Road → Pudong Airport</t>
         </is>
       </c>
       <c r="E94" s="14" t="inlineStr">
         <is>
-          <t>Be at check-in three hours before an international departure. There is a decent noodle bar airside past security in T2, and the duty-free baijiu is cheaper than the city if you want a bottle of Moutai to explain to Indian customs.</t>
+          <t>¥50 with a boarding pass (¥50 single, ¥40 with same-day air ticket). 30 km in 7 minutes 20 seconds, topping out at 431 km/h — the fastest commercial train on the planet, magnetically levitated 10 mm off the guideway. There is a speedometer in each carriage. Everybody films it. Do the 15:00–15:30 departures; they run the full-speed schedule.</t>
         </is>
       </c>
       <c r="F94" s="15" t="inlineStr">
         <is>
-          <t>Airport</t>
+          <t>Do it</t>
         </is>
       </c>
       <c r="G94" s="16" t="n">
-        <v>0</v>
+        <v>590</v>
       </c>
     </row>
     <row r="95" ht="42" customHeight="1">
@@ -3451,77 +3468,895 @@
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>18:40  Depart Shanghai → Mumbai</t>
+          <t>15:45  Pudong International (PVG), Terminal 2</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>One stop again, about 10h 15m in total, landing at CSMIA in the small hours (you gain 2h30 back). Seven days, three cities, four UNESCO World Heritage sites, and change left from a lakh.</t>
+          <t>Be at check-in three hours before an international departure. There is a decent noodle bar airside past security in T2, and the duty-free baijiu is cheaper than the city if you want a bottle of Moutai to explain to Indian customs.</t>
         </is>
       </c>
       <c r="F95" s="9" t="inlineStr">
         <is>
-          <t>Flight</t>
+          <t>Airport</t>
         </is>
       </c>
       <c r="G95" s="10" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="17" t="inlineStr"/>
-      <c r="B96" s="17" t="inlineStr"/>
-      <c r="C96" s="17" t="inlineStr"/>
-      <c r="D96" s="18" t="inlineStr">
+    <row r="96" ht="42" customHeight="1">
+      <c r="A96" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="B96" s="12" t="inlineStr">
+        <is>
+          <t>Day 7</t>
+        </is>
+      </c>
+      <c r="C96" s="12" t="inlineStr">
+        <is>
+          <t>Shanghai</t>
+        </is>
+      </c>
+      <c r="D96" s="13" t="inlineStr">
+        <is>
+          <t>18:40  Depart Shanghai → Mumbai</t>
+        </is>
+      </c>
+      <c r="E96" s="14" t="inlineStr">
+        <is>
+          <t>One stop again, about 10h 15m in total, landing at CSMIA in the small hours (you gain 2h30 back). Seven days, three cities, four UNESCO World Heritage sites, and change left from a lakh.</t>
+        </is>
+      </c>
+      <c r="F96" s="15" t="inlineStr">
+        <is>
+          <t>Flight</t>
+        </is>
+      </c>
+      <c r="G96" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="17" t="inlineStr"/>
+      <c r="B97" s="17" t="inlineStr"/>
+      <c r="C97" s="17" t="inlineStr"/>
+      <c r="D97" s="18" t="inlineStr">
         <is>
           <t>Day 7 — activities subtotal</t>
         </is>
       </c>
-      <c r="E96" s="19" t="inlineStr">
+      <c r="E97" s="19" t="inlineStr">
         <is>
           <t>Hotel that night: — (overnight flight home)</t>
         </is>
       </c>
-      <c r="F96" s="19" t="inlineStr">
+      <c r="F97" s="19" t="inlineStr">
         <is>
           <t>no hotel bill</t>
         </is>
       </c>
-      <c r="G96" s="20" t="n">
+      <c r="G97" s="20" t="n">
         <v>3590</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="21" t="inlineStr"/>
-      <c r="B98" s="21" t="inlineStr"/>
-      <c r="C98" s="21" t="inlineStr"/>
-      <c r="D98" s="22" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="21" t="inlineStr"/>
+      <c r="B99" s="21" t="inlineStr"/>
+      <c r="C99" s="21" t="inlineStr"/>
+      <c r="D99" s="22" t="inlineStr">
         <is>
           <t>ALL 7 DAYS — activities + transport</t>
         </is>
       </c>
-      <c r="E98" s="23" t="inlineStr">
+      <c r="E99" s="23" t="inlineStr">
         <is>
           <t>Hotels are on the Hotels tab; flights, visa and eSIM are on the Budget tab.</t>
         </is>
       </c>
-      <c r="F98" s="21" t="inlineStr"/>
-      <c r="G98" s="24" t="n">
-        <v>34250</v>
+      <c r="F99" s="21" t="inlineStr"/>
+      <c r="G99" s="24" t="n">
+        <v>34500</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A3:G3"/>
   <mergeCells count="9">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A74:G74"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A63:G63"/>
+    <mergeCell ref="A35:G35"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A48:G48"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A62:G62"/>
+    <mergeCell ref="A87:G87"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A86:G86"/>
+    <mergeCell ref="A49:G49"/>
+    <mergeCell ref="A75:G75"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BEIJING  ·  HOW YOU MOVE, DAY BY DAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Beijing is built on one north-south Central Axis with ring roads around it. Each day has a different shape against that grid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Stop</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Then travel by</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" s="40" t="inlineStr">
+        <is>
+          <t>DAY 1  ·  The Central Axis   —   Almost all of today is one straight walk north. From the hotel at Qianmen to the hutongs behind Jingshan is 4.2 km in a line — you cross Tiananmen Square, walk through the Forbidden City, and climb the hill behind it, all on the axis the city was built around in 1420.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="C5" s="64" t="inlineStr">
+        <is>
+          <t>Hotel, Qianmen</t>
+        </is>
+      </c>
+      <c r="D5" s="65" t="n">
+        <v>39.8994</v>
+      </c>
+      <c r="E5" s="65" t="n">
+        <v>116.3958</v>
+      </c>
+      <c r="F5" s="66" t="inlineStr">
+        <is>
+          <t>walk - 5 min, 0.4 km</t>
+        </is>
+      </c>
+      <c r="G5" s="67" t="inlineStr">
+        <is>
+          <t>Qianmen East Ave</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="C6" s="25" t="inlineStr">
+        <is>
+          <t>Siji Minfu</t>
+        </is>
+      </c>
+      <c r="D6" s="68" t="n">
+        <v>39.8998</v>
+      </c>
+      <c r="E6" s="68" t="n">
+        <v>116.4</v>
+      </c>
+      <c r="F6" s="43" t="inlineStr">
+        <is>
+          <t>walk - 12 min, 0.9 km</t>
+        </is>
+      </c>
+      <c r="G6" s="34" t="inlineStr">
+        <is>
+          <t>north up the axis</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C7" s="64" t="inlineStr">
+        <is>
+          <t>Tiananmen Square</t>
+        </is>
+      </c>
+      <c r="D7" s="65" t="n">
+        <v>39.9055</v>
+      </c>
+      <c r="E7" s="65" t="n">
+        <v>116.3976</v>
+      </c>
+      <c r="F7" s="66" t="inlineStr">
+        <is>
+          <t>walk - 4 min, 0.3 km</t>
+        </is>
+      </c>
+      <c r="G7" s="67" t="inlineStr">
+        <is>
+          <t>east side of the square</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>National Museum (optional)</t>
+        </is>
+      </c>
+      <c r="D8" s="68" t="n">
+        <v>39.9047</v>
+      </c>
+      <c r="E8" s="68" t="n">
+        <v>116.4022</v>
+      </c>
+      <c r="F8" s="43" t="inlineStr">
+        <is>
+          <t>walk - 12 min, 1 km</t>
+        </is>
+      </c>
+      <c r="G8" s="34" t="inlineStr">
+        <is>
+          <t>through the Gate of Heavenly Peace</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="C9" s="64" t="inlineStr">
+        <is>
+          <t>Forbidden City</t>
+        </is>
+      </c>
+      <c r="D9" s="65" t="n">
+        <v>39.9163</v>
+      </c>
+      <c r="E9" s="65" t="n">
+        <v>116.3972</v>
+      </c>
+      <c r="F9" s="66" t="inlineStr">
+        <is>
+          <t>walk - 6 min, 0.4 km</t>
+        </is>
+      </c>
+      <c r="G9" s="67" t="inlineStr">
+        <is>
+          <t>out of Shenwumen, cross the road</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="C10" s="25" t="inlineStr">
+        <is>
+          <t>Jingshan Park</t>
+        </is>
+      </c>
+      <c r="D10" s="68" t="n">
+        <v>39.928</v>
+      </c>
+      <c r="E10" s="68" t="n">
+        <v>116.3966</v>
+      </c>
+      <c r="F10" s="43" t="inlineStr">
+        <is>
+          <t>walk - 20 min, 1.4 km</t>
+        </is>
+      </c>
+      <c r="G10" s="34" t="inlineStr">
+        <is>
+          <t>north-east into the lanes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="C11" s="64" t="inlineStr">
+        <is>
+          <t>Nanluoguxiang hutongs</t>
+        </is>
+      </c>
+      <c r="D11" s="65" t="n">
+        <v>39.937</v>
+      </c>
+      <c r="E11" s="65" t="n">
+        <v>116.403</v>
+      </c>
+      <c r="F11" s="66" t="inlineStr">
+        <is>
+          <t>metro - 18 min, 3.4 km</t>
+        </is>
+      </c>
+      <c r="G11" s="67" t="inlineStr">
+        <is>
+          <t>Line 6 → Line 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="C12" s="25" t="inlineStr">
+        <is>
+          <t>Wangfujing</t>
+        </is>
+      </c>
+      <c r="D12" s="68" t="n">
+        <v>39.9145</v>
+      </c>
+      <c r="E12" s="68" t="n">
+        <v>116.4108</v>
+      </c>
+      <c r="F12" s="43" t="inlineStr">
+        <is>
+          <t>metro - 12 min, 2.4 km</t>
+        </is>
+      </c>
+      <c r="G12" s="34" t="inlineStr">
+        <is>
+          <t>Line 1 → Line 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="C13" s="64" t="inlineStr">
+        <is>
+          <t>Back to Qianmen</t>
+        </is>
+      </c>
+      <c r="D13" s="65" t="n">
+        <v>39.8994</v>
+      </c>
+      <c r="E13" s="65" t="n">
+        <v>116.3958</v>
+      </c>
+      <c r="F13" s="66" t="inlineStr">
+        <is>
+          <t>end of day</t>
+        </is>
+      </c>
+      <c r="G13" s="67" t="inlineStr">
+        <is>
+          <t>Sleep</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr"/>
+      <c r="B14" s="17" t="inlineStr"/>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>Day 1 totals</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="inlineStr"/>
+      <c r="E14" s="17" t="inlineStr"/>
+      <c r="F14" s="60" t="inlineStr">
+        <is>
+          <t>10.2 km covered</t>
+        </is>
+      </c>
+      <c r="G14" s="19" t="inlineStr">
+        <is>
+          <t>1h 29m in transit, 9.6 km on foot</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="40" t="inlineStr">
+        <is>
+          <t>DAY 2  ·  The Big Loop   —   The opposite shape: today you throw yourself at the two far corners of the city. Far south at dawn for the Temple of Heaven, then 24 km north-west to the Summer Palace, then 15 km east to the Olympic Park — and Line 8 brings you straight back down the same Central Axis to the hotpot. Roughly 52 km of metro, all of it for ¥16.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>06:15</t>
+        </is>
+      </c>
+      <c r="C17" s="64" t="inlineStr">
+        <is>
+          <t>Hotel, Qianmen</t>
+        </is>
+      </c>
+      <c r="D17" s="65" t="n">
+        <v>39.8994</v>
+      </c>
+      <c r="E17" s="65" t="n">
+        <v>116.3958</v>
+      </c>
+      <c r="F17" s="66" t="inlineStr">
+        <is>
+          <t>metro - 18 min, 3.2 km</t>
+        </is>
+      </c>
+      <c r="G17" s="67" t="inlineStr">
+        <is>
+          <t>Line 2 → Line 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="C18" s="25" t="inlineStr">
+        <is>
+          <t>Temple of Heaven</t>
+        </is>
+      </c>
+      <c r="D18" s="68" t="n">
+        <v>39.8822</v>
+      </c>
+      <c r="E18" s="68" t="n">
+        <v>116.4066</v>
+      </c>
+      <c r="F18" s="43" t="inlineStr">
+        <is>
+          <t>metro - 75 min, 24 km</t>
+        </is>
+      </c>
+      <c r="G18" s="34" t="inlineStr">
+        <is>
+          <t>Line 5 → Line 10 → Line 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C19" s="64" t="inlineStr">
+        <is>
+          <t>Summer Palace</t>
+        </is>
+      </c>
+      <c r="D19" s="65" t="n">
+        <v>39.9999</v>
+      </c>
+      <c r="E19" s="65" t="n">
+        <v>116.2688</v>
+      </c>
+      <c r="F19" s="66" t="inlineStr">
+        <is>
+          <t>metro - 55 min, 15.2 km</t>
+        </is>
+      </c>
+      <c r="G19" s="67" t="inlineStr">
+        <is>
+          <t>Line 4 → Line 10 → Line 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="C20" s="25" t="inlineStr">
+        <is>
+          <t>Water Cube</t>
+        </is>
+      </c>
+      <c r="D20" s="68" t="n">
+        <v>39.9925</v>
+      </c>
+      <c r="E20" s="68" t="n">
+        <v>116.3833</v>
+      </c>
+      <c r="F20" s="43" t="inlineStr">
+        <is>
+          <t>walk - 8 min, 0.6 km</t>
+        </is>
+      </c>
+      <c r="G20" s="34" t="inlineStr">
+        <is>
+          <t>across the Olympic plaza</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C21" s="64" t="inlineStr">
+        <is>
+          <t>Bird’s Nest</t>
+        </is>
+      </c>
+      <c r="D21" s="65" t="n">
+        <v>39.9928</v>
+      </c>
+      <c r="E21" s="65" t="n">
+        <v>116.3906</v>
+      </c>
+      <c r="F21" s="66" t="inlineStr">
+        <is>
+          <t>metro - 35 min, 13 km</t>
+        </is>
+      </c>
+      <c r="G21" s="67" t="inlineStr">
+        <is>
+          <t>Line 8, no changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="C22" s="25" t="inlineStr">
+        <is>
+          <t>Sesame hotpot, Qianmen</t>
+        </is>
+      </c>
+      <c r="D22" s="68" t="n">
+        <v>39.8994</v>
+      </c>
+      <c r="E22" s="68" t="n">
+        <v>116.3958</v>
+      </c>
+      <c r="F22" s="43" t="inlineStr">
+        <is>
+          <t>end of day</t>
+        </is>
+      </c>
+      <c r="G22" s="34" t="inlineStr">
+        <is>
+          <t>Line 8 straight home</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="17" t="inlineStr"/>
+      <c r="B23" s="17" t="inlineStr"/>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>Day 2 totals</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="inlineStr"/>
+      <c r="E23" s="17" t="inlineStr"/>
+      <c r="F23" s="60" t="inlineStr">
+        <is>
+          <t>56.0 km covered</t>
+        </is>
+      </c>
+      <c r="G23" s="19" t="inlineStr">
+        <is>
+          <t>3h 11m in transit, 14.8 km on foot</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="40" t="inlineStr">
+        <is>
+          <t>DAY 3  ·  North to the Wall   —   One long line north and back. Mutianyu is 70 km beyond the city on the Huairou mountain ridge, and the whole day is built around getting there before the coaches and back in time for a 20:37 train. Nothing else happens in Beijing today, on purpose.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>05:45</t>
+        </is>
+      </c>
+      <c r="C26" s="64" t="inlineStr">
+        <is>
+          <t>Hotel, Qianmen</t>
+        </is>
+      </c>
+      <c r="D26" s="65" t="n">
+        <v>39.8994</v>
+      </c>
+      <c r="E26" s="65" t="n">
+        <v>116.3958</v>
+      </c>
+      <c r="F26" s="66" t="inlineStr">
+        <is>
+          <t>metro - 15 min, 5.8 km</t>
+        </is>
+      </c>
+      <c r="G26" s="67" t="inlineStr">
+        <is>
+          <t>Line 2 anticlockwise</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="C27" s="25" t="inlineStr">
+        <is>
+          <t>Dongzhimen</t>
+        </is>
+      </c>
+      <c r="D27" s="68" t="n">
+        <v>39.9418</v>
+      </c>
+      <c r="E27" s="68" t="n">
+        <v>116.4342</v>
+      </c>
+      <c r="F27" s="43" t="inlineStr">
+        <is>
+          <t>bus - 125 min, 70 km</t>
+        </is>
+      </c>
+      <c r="G27" s="34" t="inlineStr">
+        <is>
+          <t>Bus 916 Express + h23</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="C28" s="64" t="inlineStr">
+        <is>
+          <t>Mutianyu Great Wall</t>
+        </is>
+      </c>
+      <c r="D28" s="65" t="n">
+        <v>40.4319</v>
+      </c>
+      <c r="E28" s="65" t="n">
+        <v>116.5704</v>
+      </c>
+      <c r="F28" s="66" t="inlineStr">
+        <is>
+          <t>bus - 120 min, 70 km</t>
+        </is>
+      </c>
+      <c r="G28" s="67" t="inlineStr">
+        <is>
+          <t>the same bus, reversed</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C29" s="25" t="inlineStr">
+        <is>
+          <t>Dongzhimen</t>
+        </is>
+      </c>
+      <c r="D29" s="68" t="n">
+        <v>39.9418</v>
+      </c>
+      <c r="E29" s="68" t="n">
+        <v>116.4342</v>
+      </c>
+      <c r="F29" s="43" t="inlineStr">
+        <is>
+          <t>metro - 12 min, 4.6 km</t>
+        </is>
+      </c>
+      <c r="G29" s="34" t="inlineStr">
+        <is>
+          <t>Line 2 → hotel → Line 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B30" s="12" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C30" s="64" t="inlineStr">
+        <is>
+          <t>Beijing Railway Station</t>
+        </is>
+      </c>
+      <c r="D30" s="65" t="n">
+        <v>39.9026</v>
+      </c>
+      <c r="E30" s="65" t="n">
+        <v>116.427</v>
+      </c>
+      <c r="F30" s="66" t="inlineStr">
+        <is>
+          <t>end of day</t>
+        </is>
+      </c>
+      <c r="G30" s="67" t="inlineStr">
+        <is>
+          <t>Z19 at 20:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="17" t="inlineStr"/>
+      <c r="B31" s="17" t="inlineStr"/>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>Day 3 totals</t>
+        </is>
+      </c>
+      <c r="D31" s="17" t="inlineStr"/>
+      <c r="E31" s="17" t="inlineStr"/>
+      <c r="F31" s="60" t="inlineStr">
+        <is>
+          <t>150.4 km covered</t>
+        </is>
+      </c>
+      <c r="G31" s="19" t="inlineStr">
+        <is>
+          <t>4h 32m in transit, 10.4 km on foot</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A25:G25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3642,14 +4477,14 @@
         </is>
       </c>
       <c r="C6" s="27" t="n">
-        <v>12810</v>
+        <v>13140</v>
       </c>
       <c r="D6" s="28" t="n">
-        <v>0.1281</v>
+        <v>0.1314</v>
       </c>
       <c r="E6" s="29" t="inlineStr">
         <is>
-          <t>The four UNESCO sites are ₹4,560 of this. Every rupee is itemised in the day plans.</t>
+          <t>Six UNESCO sites now — the Summer Palace and the Temple of Heaven are ₹1,130 of this. Every rupee is itemised in the day plans.</t>
         </is>
       </c>
     </row>
@@ -3688,14 +4523,14 @@
         </is>
       </c>
       <c r="C8" s="27" t="n">
-        <v>7510</v>
+        <v>7320</v>
       </c>
       <c r="D8" s="28" t="n">
-        <v>0.0751</v>
+        <v>0.0732</v>
       </c>
       <c r="E8" s="29" t="inlineStr">
         <is>
-          <t>≈₹1,070/day. Street breakfasts, one big meal a day — Peking duck and hotpot included.</t>
+          <t>≈₹1,045/day. Street breakfasts, one big meal a day — Peking duck and sesame hotpot included.</t>
         </is>
       </c>
     </row>
@@ -3711,14 +4546,14 @@
         </is>
       </c>
       <c r="C9" s="27" t="n">
-        <v>2590</v>
+        <v>2700</v>
       </c>
       <c r="D9" s="28" t="n">
-        <v>0.0259</v>
+        <v>0.027</v>
       </c>
       <c r="E9" s="29" t="inlineStr">
         <is>
-          <t>Chinese metro rides cost ₹35–70. The 431 km/h Maglev is ₹590 of this and worth it.</t>
+          <t>Chinese metro rides cost ₹35–70, and Day 2 crosses the whole city twice. The 431 km/h Maglev is ₹590 of this.</t>
         </is>
       </c>
     </row>
@@ -3780,14 +4615,14 @@
         </is>
       </c>
       <c r="C12" s="27" t="n">
-        <v>9450</v>
+        <v>9200</v>
       </c>
       <c r="D12" s="28" t="n">
-        <v>0.0945</v>
+        <v>0.092</v>
       </c>
       <c r="E12" s="29" t="inlineStr">
         <is>
-          <t>Real slack: ₹1,600 earmarked for souvenirs, ₹7,850 of genuine untouched buffer.</t>
+          <t>Real slack: ₹1,600 earmarked for souvenirs, ₹7,600 of genuine untouched buffer.</t>
         </is>
       </c>
     </row>
@@ -3829,7 +4664,7 @@
         </is>
       </c>
       <c r="C16" s="35" t="n">
-        <v>34250</v>
+        <v>34500</v>
       </c>
       <c r="D16" s="6" t="inlineStr"/>
       <c r="E16" s="6" t="inlineStr"/>
@@ -3880,7 +4715,7 @@
         </is>
       </c>
       <c r="C19" s="35" t="n">
-        <v>92150</v>
+        <v>92400</v>
       </c>
       <c r="D19" s="6" t="inlineStr"/>
       <c r="E19" s="6" t="inlineStr"/>
@@ -3897,7 +4732,7 @@
         </is>
       </c>
       <c r="C20" s="36" t="n">
-        <v>7850</v>
+        <v>7600</v>
       </c>
       <c r="D20" s="6" t="inlineStr"/>
       <c r="E20" s="6" t="inlineStr"/>
@@ -6331,7 +7166,7 @@
       </c>
       <c r="B4" s="63" t="inlineStr">
         <is>
-          <t>Yes, with discipline and this exact structure. Flights eat ₹38,000, leaving ₹62,000 for the ground — which is comfortable in China if you stay in central 3★ hotels, use trains rather than internal flights, eat street breakfasts and take the public bus to the Great Wall. The plan as written lands at ₹92,150 — ₹47,550 on the ground plus ₹44,600 of flights, visa, insurance and eSIM — leaving ₹7,850 of real buffer. The two things that will blow it are booking flights late and taking taxis everywhere.</t>
+          <t>Yes, with discipline and this exact structure. Flights eat ₹38,000, leaving ₹62,000 for the ground — which is comfortable in China if you stay in central 3★ hotels, use trains rather than internal flights, eat street breakfasts and take the public bus to the Great Wall. The plan as written lands at ₹92,400 — ₹47,800 on the ground plus ₹44,600 of flights, visa, insurance and eSIM — leaving ₹7,600 of real buffer. The two things that will blow it are booking flights late and taking taxis everywhere.</t>
         </is>
       </c>
     </row>
